--- a/mlef_pipeline/results/OS_24/SQUAMOUS/RWD_FMRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/OS_24/SQUAMOUS/RWD_FMRAD/rwd-only/results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.57 ± 0.13</t>
+          <t>0.67 ± 0.14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.43 ± 0.09</t>
+          <t>0.51 ± 0.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.33 ± 0.38</t>
+          <t>0.65 ± 0.30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.74 ± 0.31</t>
+          <t>0.63 ± 0.34</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.62 ± 0.22</t>
+          <t>0.60 ± 0.24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.86 ± nan</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>1.00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.29</t>
         </is>
       </c>
       <c r="F4" t="n">

--- a/mlef_pipeline/results/OS_24/SQUAMOUS/RWD_FMRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/OS_24/SQUAMOUS/RWD_FMRAD/rwd-only/results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
